--- a/ver4/tree.xlsx
+++ b/ver4/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\6\family-tree-desktop_6_03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25230" windowHeight="8235" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="353">
   <si>
     <t>idA</t>
   </si>
@@ -1086,6 +1086,9 @@
   </si>
   <si>
     <t>https://proza.ru/2025/03/17/154 ; https://zwiahel.ucoz.ru/novograd/evrei/lenin_01.html</t>
+  </si>
+  <si>
+    <t>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</t>
   </si>
 </sst>
 </file>
@@ -2383,8 +2386,8 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f>B2&amp;"-"&amp;C2</f>
-        <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна</v>
+        <f>B2&amp;"__"&amp;C2</f>
+        <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>22</v>
@@ -2403,9 +2406,9 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <f>B3&amp;"-"&amp;C3</f>
-        <v>Бланк_Александр_Дмитриевич-Гроссшопф_Анна_Ивановна</v>
+      <c r="A3" s="7" t="str">
+        <f t="shared" ref="A3:A6" si="0">B3&amp;"__"&amp;C3</f>
+        <v>Бланк_Александр_Дмитриевич__Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2424,9 +2427,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
-        <f>B4&amp;"-"&amp;C4</f>
-        <v>Ульянов_Владимир_Ильич-Крупская_Надежда_Константиновна</v>
+      <c r="A4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Ульянов_Владимир_Ильич__Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B4" t="s">
         <v>150</v>
@@ -2449,8 +2452,8 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="str">
-        <f>B5&amp;"-"&amp;C5</f>
-        <v>Ульянин_Николай_Васильевич-Смирнова_Анна_Алексеевна</v>
+        <f t="shared" si="0"/>
+        <v>Ульянин_Николай_Васильевич__Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -2473,8 +2476,8 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="str">
-        <f>B6&amp;"-"&amp;C6</f>
-        <v>Бланк_Александр_Дмитриевич-Эссен_Екатерина_Ивановна</v>
+        <f t="shared" si="0"/>
+        <v>Бланк_Александр_Дмитриевич__Эссен_Екатерина_Ивановна</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>44</v>
@@ -2711,7 +2714,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>352</v>
       </c>
       <c r="B2">
         <v>1879</v>
@@ -2721,7 +2724,7 @@
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна-1879.jpg</v>
+        <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
         <v>174</v>

--- a/ver4/tree.xlsx
+++ b/ver4/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="357">
   <si>
     <t>idA</t>
   </si>
@@ -1089,6 +1089,18 @@
   </si>
   <si>
     <t>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</t>
+  </si>
+  <si>
+    <t>husband_</t>
+  </si>
+  <si>
+    <t>wife_</t>
+  </si>
+  <si>
+    <t>Муж</t>
+  </si>
+  <si>
+    <t>Жена</t>
   </si>
 </sst>
 </file>
@@ -2351,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>353</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>
@@ -3263,7 +3275,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="7" customWidth="1"/>
@@ -4060,6 +4072,40 @@
       </c>
       <c r="E46" t="s">
         <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/ver4/tree.xlsx
+++ b/ver4/tree.xlsx
@@ -782,9 +782,6 @@
     <t>occupation</t>
   </si>
   <si>
-    <t>число детей</t>
-  </si>
-  <si>
     <t>children count</t>
   </si>
   <si>
@@ -1101,6 +1098,9 @@
   </si>
   <si>
     <t>Жена</t>
+  </si>
+  <si>
+    <t>число детей:</t>
   </si>
 </sst>
 </file>
@@ -1785,10 +1785,10 @@
         <v>24</v>
       </c>
       <c r="J7" t="s">
+        <v>344</v>
+      </c>
+      <c r="K7" t="s">
         <v>345</v>
-      </c>
-      <c r="K7" t="s">
-        <v>346</v>
       </c>
       <c r="O7" t="s">
         <v>63</v>
@@ -2316,7 +2316,7 @@
         <v>Эссен_Екатерина_Ивановна</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>42</v>
@@ -2325,7 +2325,7 @@
         <v>1863</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>
@@ -2495,13 +2495,13 @@
         <v>44</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B2">
         <v>1879</v>
@@ -4017,10 +4017,10 @@
         <v>142</v>
       </c>
       <c r="D43" t="s">
+        <v>356</v>
+      </c>
+      <c r="E43" t="s">
         <v>250</v>
-      </c>
-      <c r="E43" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -4034,10 +4034,10 @@
         <v>143</v>
       </c>
       <c r="D44" t="s">
+        <v>251</v>
+      </c>
+      <c r="E44" t="s">
         <v>252</v>
-      </c>
-      <c r="E44" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -4051,10 +4051,10 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" t="s">
         <v>254</v>
-      </c>
-      <c r="E45" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -4068,10 +4068,10 @@
         <v>144</v>
       </c>
       <c r="D46" t="s">
+        <v>255</v>
+      </c>
+      <c r="E46" t="s">
         <v>256</v>
-      </c>
-      <c r="E46" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -4082,10 +4082,10 @@
         <v>227</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>136</v>
@@ -4099,10 +4099,10 @@
         <v>227</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>137</v>
@@ -4125,13 +4125,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4139,7 +4139,7 @@
         <v>216</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4161,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4172,7 +4172,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4183,7 +4183,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,7 +4194,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4216,7 +4216,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4227,7 +4227,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4238,7 +4238,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4249,7 +4249,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4271,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4282,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4315,7 +4315,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4326,7 +4326,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4337,7 +4337,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4348,7 +4348,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4356,7 +4356,7 @@
         <v>227</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4378,7 +4378,7 @@
         <v>136</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4389,7 +4389,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -4400,7 +4400,7 @@
         <v>138</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -4411,7 +4411,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -4422,7 +4422,7 @@
         <v>139</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>140</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,7 +4444,7 @@
         <v>141</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,7 +4466,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,7 +4477,7 @@
         <v>142</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,7 +4488,7 @@
         <v>143</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -4496,7 +4496,7 @@
         <v>197</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -4507,7 +4507,7 @@
         <v>156</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4518,7 +4518,7 @@
         <v>157</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4529,7 +4529,7 @@
         <v>158</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4551,7 +4551,7 @@
         <v>159</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -4562,7 +4562,7 @@
         <v>160</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>161</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -4584,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -4595,7 +4595,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -4603,7 +4603,7 @@
         <v>198</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -4614,7 +4614,7 @@
         <v>166</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -4625,7 +4625,7 @@
         <v>167</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -4636,7 +4636,7 @@
         <v>158</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -4658,7 +4658,7 @@
         <v>159</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>168</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -4680,7 +4680,7 @@
         <v>169</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -4691,7 +4691,7 @@
         <v>170</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -4702,7 +4702,7 @@
         <v>160</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -4713,7 +4713,7 @@
         <v>161</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -4724,7 +4724,7 @@
         <v>171</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -4735,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -4746,7 +4746,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -4757,7 +4757,7 @@
         <v>172</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,7 +4765,7 @@
         <v>199</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -4776,7 +4776,7 @@
         <v>156</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>167</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>158</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>159</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -4831,7 +4831,7 @@
         <v>172</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,7 +4842,7 @@
         <v>160</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>161</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -4864,7 +4864,7 @@
         <v>171</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -4875,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -4894,7 +4894,7 @@
         <v>200</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -4905,7 +4905,7 @@
         <v>186</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -4916,7 +4916,7 @@
         <v>157</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -4927,7 +4927,7 @@
         <v>158</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -4949,7 +4949,7 @@
         <v>159</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>187</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -4971,7 +4971,7 @@
         <v>172</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>188</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>160</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -5004,7 +5004,7 @@
         <v>161</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -5015,7 +5015,7 @@
         <v>171</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -5037,7 +5037,7 @@
         <v>10</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5048,7 +5048,7 @@
         <v>189</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -5056,7 +5056,7 @@
         <v>240</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -5067,7 +5067,7 @@
         <v>195</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -5078,7 +5078,7 @@
         <v>196</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -5089,7 +5089,7 @@
         <v>172</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -5100,7 +5100,7 @@
         <v>188</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -5111,7 +5111,7 @@
         <v>159</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -5122,7 +5122,7 @@
         <v>160</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5133,7 +5133,7 @@
         <v>161</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5144,7 +5144,7 @@
         <v>171</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -5166,7 +5166,7 @@
         <v>10</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -5177,7 +5177,7 @@
         <v>197</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -5188,7 +5188,7 @@
         <v>198</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5199,7 +5199,7 @@
         <v>199</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,70 +5210,70 @@
         <v>200</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>337</v>
+      </c>
+      <c r="C102" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s">
         <v>210</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s">
         <v>211</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s">
         <v>212</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B106" t="s">
         <v>213</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s">
         <v>214</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/ver4/tree.xlsx
+++ b/ver4/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>

--- a/ver4/tree.xlsx
+++ b/ver4/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -2685,7 +2685,7 @@
         <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>158</v>
@@ -2839,7 +2839,7 @@
         <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>158</v>
